--- a/Roster_Flight_Numbers.xlsx
+++ b/Roster_Flight_Numbers.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Notes" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Operated (freighter)'!$A$1:$H$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Operated (freighter)'!$A$1:$I$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Positioning'!$A$1:$G$89</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Patterns'!$A$2:$L$71</definedName>
   </definedNames>
@@ -545,7 +545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -556,6 +556,7 @@
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="9" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -599,6 +600,11 @@
           <t>Network</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Crew</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -641,6 +647,9 @@
           <t>Domestic</t>
         </is>
       </c>
+      <c r="I2" s="2" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -683,6 +692,9 @@
           <t>Domestic</t>
         </is>
       </c>
+      <c r="I3" s="2" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -725,6 +737,9 @@
           <t>Domestic</t>
         </is>
       </c>
+      <c r="I4" s="2" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -767,6 +782,9 @@
           <t>Domestic</t>
         </is>
       </c>
+      <c r="I5" s="2" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -809,6 +827,9 @@
           <t>Domestic</t>
         </is>
       </c>
+      <c r="I6" s="2" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -851,6 +872,9 @@
           <t>Domestic</t>
         </is>
       </c>
+      <c r="I7" s="2" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -893,6 +917,9 @@
           <t>Domestic</t>
         </is>
       </c>
+      <c r="I8" s="2" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -935,6 +962,9 @@
           <t>Domestic</t>
         </is>
       </c>
+      <c r="I9" s="2" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -977,6 +1007,9 @@
           <t>Domestic</t>
         </is>
       </c>
+      <c r="I10" s="2" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1019,6 +1052,9 @@
           <t>Domestic</t>
         </is>
       </c>
+      <c r="I11" s="2" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1061,6 +1097,9 @@
           <t>Domestic</t>
         </is>
       </c>
+      <c r="I12" s="2" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1103,6 +1142,9 @@
           <t>Domestic</t>
         </is>
       </c>
+      <c r="I13" s="2" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1145,6 +1187,9 @@
           <t>Domestic</t>
         </is>
       </c>
+      <c r="I14" s="2" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1187,6 +1232,9 @@
           <t>Domestic</t>
         </is>
       </c>
+      <c r="I15" s="2" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1229,6 +1277,9 @@
           <t>Domestic</t>
         </is>
       </c>
+      <c r="I16" s="2" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1271,6 +1322,9 @@
           <t>Domestic</t>
         </is>
       </c>
+      <c r="I17" s="2" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1313,6 +1367,9 @@
           <t>Domestic</t>
         </is>
       </c>
+      <c r="I18" s="2" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1355,6 +1412,9 @@
           <t>Domestic</t>
         </is>
       </c>
+      <c r="I19" s="2" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1397,6 +1457,9 @@
           <t>Domestic</t>
         </is>
       </c>
+      <c r="I20" s="2" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1439,6 +1502,9 @@
           <t>Domestic</t>
         </is>
       </c>
+      <c r="I21" s="2" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1481,6 +1547,9 @@
           <t>International</t>
         </is>
       </c>
+      <c r="I22" s="14" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1523,6 +1592,9 @@
           <t>International</t>
         </is>
       </c>
+      <c r="I23" s="14" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1565,6 +1637,9 @@
           <t>International</t>
         </is>
       </c>
+      <c r="I24" s="2" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -1607,6 +1682,9 @@
           <t>International</t>
         </is>
       </c>
+      <c r="I25" s="14" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -1649,6 +1727,9 @@
           <t>International</t>
         </is>
       </c>
+      <c r="I26" s="2" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -1691,6 +1772,9 @@
           <t>International</t>
         </is>
       </c>
+      <c r="I27" s="2" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -1733,6 +1817,9 @@
           <t>International</t>
         </is>
       </c>
+      <c r="I28" s="2" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -1775,6 +1862,9 @@
           <t>International</t>
         </is>
       </c>
+      <c r="I29" s="2" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -1817,9 +1907,12 @@
           <t>International</t>
         </is>
       </c>
+      <c r="I30" s="2" t="n">
+        <v>2</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H30"/>
+  <autoFilter ref="A1:I30"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5483,6 +5576,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
         <is>
@@ -5645,6 +5739,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
         <is>
@@ -5807,6 +5902,7 @@
         </is>
       </c>
     </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
@@ -6054,13 +6150,13 @@
       <c r="L21" s="13" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr"/>
       <c r="B22" s="16" t="inlineStr">
         <is>
           <t>International pairing</t>
         </is>
       </c>
     </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
         <is>
@@ -6258,13 +6354,13 @@
       <c r="L27" s="13" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr"/>
       <c r="B28" s="16" t="inlineStr">
         <is>
           <t>Positions home</t>
         </is>
       </c>
     </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" s="12" t="inlineStr">
         <is>
@@ -6369,6 +6465,7 @@
         </is>
       </c>
     </row>
+    <row r="32"/>
     <row r="33">
       <c r="A33" s="12" t="inlineStr">
         <is>
@@ -6469,6 +6566,7 @@
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="13" t="inlineStr"/>
     </row>
+    <row r="35"/>
     <row r="36">
       <c r="A36" s="12" t="inlineStr">
         <is>
@@ -6616,13 +6714,13 @@
       <c r="L38" s="13" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr"/>
       <c r="B39" s="16" t="inlineStr">
         <is>
           <t>Positions home</t>
         </is>
       </c>
     </row>
+    <row r="40"/>
     <row r="41">
       <c r="A41" s="12" t="inlineStr">
         <is>
@@ -6770,13 +6868,13 @@
       <c r="L43" s="13" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr"/>
       <c r="B44" s="16" t="inlineStr">
         <is>
           <t>3rd crew member</t>
         </is>
       </c>
     </row>
+    <row r="45"/>
     <row r="46">
       <c r="A46" s="12" t="inlineStr">
         <is>
@@ -6920,13 +7018,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr"/>
       <c r="B49" s="16" t="inlineStr">
         <is>
           <t>Positions home via HKG</t>
         </is>
       </c>
     </row>
+    <row r="50"/>
     <row r="51">
       <c r="A51" s="12" t="inlineStr">
         <is>
@@ -7132,13 +7230,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr"/>
       <c r="B55" s="16" t="inlineStr">
         <is>
           <t>Positioning start from MEL</t>
         </is>
       </c>
     </row>
+    <row r="56"/>
     <row r="57">
       <c r="A57" s="12" t="inlineStr">
         <is>
@@ -7332,13 +7430,13 @@
       <c r="L60" s="13" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr"/>
       <c r="B61" s="16" t="inlineStr">
         <is>
           <t>Positioning start from MEL</t>
         </is>
       </c>
     </row>
+    <row r="62"/>
     <row r="63">
       <c r="A63" s="12" t="inlineStr">
         <is>
@@ -7532,13 +7630,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr"/>
       <c r="B67" s="16" t="inlineStr">
         <is>
           <t>Positioning start via HKG/PVG</t>
         </is>
       </c>
     </row>
+    <row r="68"/>
     <row r="69">
       <c r="A69" s="12" t="inlineStr">
         <is>
@@ -7644,7 +7742,6 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr"/>
       <c r="B71" s="16" t="inlineStr">
         <is>
           <t>Positioning start via SIN</t>
@@ -7663,7 +7760,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -7717,38 +7814,50 @@
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>Positioning tab</t>
+          <t>Crew</t>
         </is>
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>Unchanged — deadhead / passenger travel to &amp; from freighter duties (QF, Cathay CX, Japan Airlines JL); scheduled times from public sources.</t>
+          <t>Crew complement. 3 = augmented (Z crew, 3rd pilot) — QF7525, QF7526 and QF7535 are the only flights operated augmented; every other flight is 2. Drives the standby call-out limit in index.html: 16 h from the start of standby to the end of the FDP on 2 crew, 20 h on 3.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
         <is>
+          <t>Positioning tab</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>Unchanged — deadhead / passenger travel to &amp; from freighter duties (QF, Cathay CX, Japan Airlines JL); scheduled times from public sources.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
           <t>Check</t>
         </is>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>International day columns in the photo are small — verify 7525/7526/7531/7535/7536 day patterns if precision matters.</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="10" t="inlineStr"/>
-      <c r="B7" s="10" t="inlineStr"/>
-    </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr"/>
+      <c r="B8" s="10" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>Counts</t>
         </is>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>Operated (freighter): 29 rows  |  Positioning: 120 rows</t>
         </is>
